--- a/output/pdf_financials_xlsx/RSG.xlsx
+++ b/output/pdf_financials_xlsx/RSG.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013643</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00645</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001308</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000417</v>
       </c>
     </row>
     <row r="13">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.527284</v>
+        <v>-1.513641</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.259398</v>
+        <v>-1.252948</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.855042</v>
+        <v>-3.853734</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.687793</v>
+        <v>-2.687376</v>
       </c>
     </row>
     <row r="28">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.512645</v>
+        <v>-1.499002</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.249483</v>
+        <v>-1.243033</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.85359</v>
+        <v>-3.852282</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.687503</v>
+        <v>-2.687086</v>
       </c>
     </row>
     <row r="30">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">

--- a/output/pdf_financials_xlsx/RSG.xlsx
+++ b/output/pdf_financials_xlsx/RSG.xlsx
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.000242</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>5.9e-05</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5722,7 +5722,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.000242</v>
       </c>
